--- a/unit9_watchdog/unit9_watchdog.xlsx
+++ b/unit9_watchdog/unit9_watchdog.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84CADE32-C8A7-4987-9E9F-D31F1E631CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>templater driver</t>
   </si>
@@ -43,102 +44,591 @@
     <t>sudo unmount /media/rootfs/</t>
   </si>
   <si>
-    <t>sliding window</t>
-  </si>
-  <si>
-    <t>LSTM</t>
-  </si>
-  <si>
-    <t>xử lý song song nhiều chuỗi</t>
-  </si>
-  <si>
     <t>driver thì user và kernel sẽ có các hàm quy chuẩn để giao tiếp riêng, nhưng cơ bản user sẽ thường gọi hàm read/write và kernel sẽ thực hiện thao tác đọc file device và thực hiện các lệnh tương ứng</t>
   </si>
   <si>
     <t>-&gt; SysTem call</t>
   </si>
   <si>
-    <t>Với chuỗi có 25 case, và yêu cầu mỗi mẫu gồm:</t>
-  </si>
-  <si>
-    <t>20 case đầu vào</t>
-  </si>
-  <si>
-    <t>1 case đầu ra (ngay sau đó)</t>
-  </si>
-  <si>
-    <t>Thì bạn sẽ tạo được các mẫu như sau:</t>
-  </si>
-  <si>
-    <t>Mẫu</t>
-  </si>
-  <si>
-    <t>Input (case #)</t>
-  </si>
-  <si>
-    <t>Output (case #)</t>
-  </si>
-  <si>
-    <t>1 → 20</t>
-  </si>
-  <si>
-    <t>2 → 21</t>
-  </si>
-  <si>
-    <t>3 → 22</t>
-  </si>
-  <si>
-    <t>4 → 23</t>
-  </si>
-  <si>
-    <t>5 → 24</t>
-  </si>
-  <si>
-    <t>Nếu bạn có nhiều chuỗi như vậy, mình có thể giúp bạn viết một hàm Python để:</t>
-  </si>
-  <si>
-    <t>Nhận vào danh sách các chuỗi (mỗi chuỗi là list 25 nhãn)</t>
-  </si>
-  <si>
-    <t>Trả về toàn bộ các cặp (input, output) theo đúng logic bạn mô tả</t>
-  </si>
-  <si>
-    <t>Bạn có muốn mình tạo đoạn mã đó cho bạn không?</t>
-  </si>
-  <si>
-    <t>Vâng, bạn hiểu hoàn toàn đúng!</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">👉 Tổng cộng: </t>
+    <t xml:space="preserve">protocal driver </t>
+  </si>
+  <si>
+    <t>platporm driver</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dưới đây là phần tổng quan ngắn gọn và đầy đủ về </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>5 mẫu huấn luyện</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">protocal driver </t>
-  </si>
-  <si>
-    <t>platporm driver</t>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Watchdog</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> trên </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BeagleBone Black (BBB)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t>🐶 Watchdog trong BeagleBone Black (BBB)</t>
+  </si>
+  <si>
+    <t>🧠 Watchdog là gì?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Watchdog timer (WDT) là một bộ đếm thời gian phần cứng tự động </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>reset hệ thống nếu không được “đá” (kick) định kỳ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Dùng để phát hiện và xử lý </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>treo hệ thống</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>⚙️ Phần cứng Watchdog trong BBB</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">BeagleBone Black dùng SoC </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TI AM335x</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, có </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hai Watchdog timer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>WDT1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Dùng để </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>reset hệ thống</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (system watchdog).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>WDT2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Thường </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>không được sử dụng</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> mặc định.</t>
+    </r>
+  </si>
+  <si>
+    <t>🔌 Sơ đồ kết nối</t>
+  </si>
+  <si>
+    <t>WDT1 được kết nối trực tiếp với module reset của AM335x.</t>
+  </si>
+  <si>
+    <t>Có thể kích hoạt reset cứng (cold reboot) nếu WDT timeout.</t>
+  </si>
+  <si>
+    <t>📁 Device Tree</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Trong file </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>.dts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, Watchdog thường khai báo như sau:</t>
+    </r>
+  </si>
+  <si>
+    <t>wdt@44e35000 {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    compatible = "ti,omap3-wdt";</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    reg = &lt;0x44e35000 0x1000&gt;;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    interrupts = &lt;18&gt;;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    timeout-sec = &lt;60&gt;;</t>
+  </si>
+  <si>
+    <t>};</t>
+  </si>
+  <si>
+    <t>🧰 Driver trong Linux</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dùng driver </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>omap_wdt.c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>drivers/watchdog/omap_wdt.c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sử dụng framework </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>watchdog</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> của Linux (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>include/linux/watchdog.h</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>💻 Cách sử dụng từ người dùng</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sử dụng thông qua </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>user-space</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> bằng cách:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1. Enable module</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t>modprobe omap_wdt</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. Dùng tiện ích </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>watchdog</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hoặc </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>systemd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t>apt install watchdog</t>
+  </si>
+  <si>
+    <t>systemctl enable watchdog</t>
+  </si>
+  <si>
+    <t>systemctl start watchdog</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. Hoặc dùng API </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/dev/watchdog</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t>int fd = open("/dev/watchdog", O_RDWR);</t>
+  </si>
+  <si>
+    <t>write(fd, "V", 1); // Đá watchdog</t>
+  </si>
+  <si>
+    <t>close(fd);</t>
+  </si>
+  <si>
+    <t>🛑 Reset khi hệ thống treo</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nếu ứng dụng không đá watchdog trong khoảng thời gian định sẵn (timeout), WDT sẽ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>reset hệ thống</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để khôi phục trạng thái hoạt động.</t>
+    </r>
+  </si>
+  <si>
+    <t>✅ Tóm tắt</t>
+  </si>
+  <si>
+    <t>Thành phần</t>
+  </si>
+  <si>
+    <t>Mô tả</t>
+  </si>
+  <si>
+    <t>WDT1</t>
+  </si>
+  <si>
+    <t>Watchdog chính trong BBB</t>
+  </si>
+  <si>
+    <t>Driver</t>
+  </si>
+  <si>
+    <t>omap_wdt</t>
+  </si>
+  <si>
+    <t>Thiết bị</t>
+  </si>
+  <si>
+    <t>/dev/watchdog</t>
+  </si>
+  <si>
+    <t>Công dụng</t>
+  </si>
+  <si>
+    <t>Tự động reset khi hệ thống treo</t>
+  </si>
+  <si>
+    <t>Cấu hình</t>
+  </si>
+  <si>
+    <t>Device Tree + user-space tools</t>
+  </si>
+  <si>
+    <t>Nếu bạn muốn ví dụ cấu hình đầy đủ hoặc viết chương trình C nhỏ để đá watchdog, mình có thể cung cấp thêm!</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -160,17 +650,39 @@
       <name val="Inherit"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Segoe UI"/>
+      <name val="Arial"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="1"/>
-      <name val="Segoe UI"/>
+      <name val="Arial"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -181,7 +693,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -189,53 +701,41 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -271,7 +771,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -309,7 +815,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2"/>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -347,7 +859,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4"/>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -385,7 +903,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5"/>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -423,7 +947,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6"/>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -711,9 +1241,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:J113"/>
-  <sheetFormatPr defaultColWidth="3.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="3.09765625" defaultRowHeight="13.8"/>
   <sheetData>
     <row r="2" spans="3:10">
       <c r="C2" t="s">
@@ -750,24 +1280,24 @@
         <v>6</v>
       </c>
     </row>
-    <row r="109" spans="2:5">
-      <c r="B109" s="4" t="s">
-        <v>10</v>
+    <row r="109" spans="2:5" ht="15">
+      <c r="B109" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="110" spans="2:5">
-      <c r="C110" s="5" t="s">
-        <v>11</v>
+      <c r="C110" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="112" spans="2:5">
       <c r="B112" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="113" spans="2:2">
       <c r="B113" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -778,166 +1308,280 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:C91"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="17.25">
-      <c r="A1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="17.25">
-      <c r="A2" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="17.25">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="16.5">
-      <c r="B5" s="6" t="s">
+    <row r="1" spans="1:2" ht="19.2">
+      <c r="A1" s="1"/>
+    </row>
+    <row r="2" spans="1:2" ht="19.2">
+      <c r="A2" s="2"/>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="19.2">
+      <c r="A3" s="1"/>
+    </row>
+    <row r="6" spans="1:2" ht="22.8">
+      <c r="B6" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="17.399999999999999">
+      <c r="B8" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="17.399999999999999">
+      <c r="B14" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" s="5"/>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" s="5"/>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" ht="17.399999999999999">
+      <c r="B24" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" s="5"/>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27" s="5"/>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" ht="17.399999999999999">
+      <c r="B32" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" s="9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" s="9" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
-      <c r="B6" s="3"/>
-    </row>
-    <row r="7" spans="1:4" ht="16.5">
-      <c r="B7" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="B8" s="7"/>
-    </row>
-    <row r="9" spans="1:4" ht="16.5">
-      <c r="B9" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="16.5">
-      <c r="B10" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="B11" s="3"/>
-    </row>
-    <row r="12" spans="1:4" ht="16.5">
-      <c r="B12" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="B13" s="3"/>
-    </row>
-    <row r="14" spans="1:4" ht="33">
-      <c r="B14" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="16.5">
-      <c r="B15" s="11">
-        <v>1</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="11">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="16.5">
-      <c r="B16" s="11">
-        <v>2</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="11">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" ht="16.5">
-      <c r="B17" s="11">
-        <v>3</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" s="11">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" ht="16.5">
-      <c r="B18" s="11">
-        <v>4</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="11">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" ht="16.5">
-      <c r="B19" s="11">
-        <v>5</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D19" s="11">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4">
-      <c r="B20" s="3"/>
-    </row>
-    <row r="21" spans="2:4" ht="16.5">
-      <c r="B21" s="6" t="s">
+    <row r="41" spans="2:2">
+      <c r="B41" s="9" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="2:4">
-      <c r="B22" s="3"/>
-    </row>
-    <row r="24" spans="2:4">
-      <c r="B24" s="3"/>
-    </row>
-    <row r="25" spans="2:4" ht="16.5">
-      <c r="B25" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4">
-      <c r="B26" s="7"/>
-    </row>
-    <row r="27" spans="2:4" ht="16.5">
-      <c r="B27" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4" ht="16.5">
-      <c r="B28" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4">
-      <c r="B29" s="3"/>
-    </row>
-    <row r="30" spans="2:4" ht="16.5">
-      <c r="B30" s="6" t="s">
-        <v>27</v>
+    <row r="45" spans="2:2" ht="17.399999999999999">
+      <c r="B45" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2">
+      <c r="B46" s="5"/>
+    </row>
+    <row r="47" spans="2:2">
+      <c r="B47" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2">
+      <c r="B48" s="5"/>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" ht="17.399999999999999">
+      <c r="B53" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2">
+      <c r="B55" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2">
+      <c r="B56" s="5"/>
+    </row>
+    <row r="57" spans="2:2">
+      <c r="B57" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2">
+      <c r="B59" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2">
+      <c r="B60" s="5"/>
+    </row>
+    <row r="61" spans="2:2">
+      <c r="B61" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2">
+      <c r="B63" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2">
+      <c r="B64" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2">
+      <c r="B65" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66" s="5"/>
+    </row>
+    <row r="67" spans="2:2">
+      <c r="B67" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2">
+      <c r="B69" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2">
+      <c r="B70" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2">
+      <c r="B71" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2" ht="17.399999999999999">
+      <c r="B75" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2">
+      <c r="B77" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3" ht="17.399999999999999">
+      <c r="B81" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="83" spans="2:3" ht="27.6">
+      <c r="B83" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C83" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="84" spans="2:3" ht="55.2">
+      <c r="B84" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C84" s="11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="85" spans="2:3">
+      <c r="B85" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="86" spans="2:3" ht="26.4">
+      <c r="B86" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C86" s="12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="87" spans="2:3" ht="55.2">
+      <c r="B87" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C87" s="11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="88" spans="2:3" ht="69">
+      <c r="B88" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" s="11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="91" spans="2:3">
+      <c r="B91" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
